--- a/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3004" uniqueCount="709">
   <si>
     <t>Notes</t>
   </si>
@@ -1565,6 +1565,606 @@
   </si>
   <si>
     <t>Thu Nov 20 19:26:46 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:08:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:09:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:10:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:11:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:12:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:12:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:13:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:14:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:14:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:15:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:16:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:16:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:17:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:20:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:25:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 20:59:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 21:01:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 21:02:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 21:03:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 21:04:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 21:04:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:11:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:12:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:13:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:13:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:14:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:15:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:16:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:17:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:18:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:19:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:20:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:20:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:21:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:22:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:23:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:08:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:11:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:17:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:19:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:22:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:25:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:26:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:27:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:28:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:29:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:29:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:30:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:31:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:32:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:33:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:35:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:36:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:40:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:41:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:42:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:43:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:43:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:44:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:42:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:43:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:44:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:45:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:46:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:47:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:48:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:50:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:51:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:53:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:53:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:54:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:56:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:57:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 22:58:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:00:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:03:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:04:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:05:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:06:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:07:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:07:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:08:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:09:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:10:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:11:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:12:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:13:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:13:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:14:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:15:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:16:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:34:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:35:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:36:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:37:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:38:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:39:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:39:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:40:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:41:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:42:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:43:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:43:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:44:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:45:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:46:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:47:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:26:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:27:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:28:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:30:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:31:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:33:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:34:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:35:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:37:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:38:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:39:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:40:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:43:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:44:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:45:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:14:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:15:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:16:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:17:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:18:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:19:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:21:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:22:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:23:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:23:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:24:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:25:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:26:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:27:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:28:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:29:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:16:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:17:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:18:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:18:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:20:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:21:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:22:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:23:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:24:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:24:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:25:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:26:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:27:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:28:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:28:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:00:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:01:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:02:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:03:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:04:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:05:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:05:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:06:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:08:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:08:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:09:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:10:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:11:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:12:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:12:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:13:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:14:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:15:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:15:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:16:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:41:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:42:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:42:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:43:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:44:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:46:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:47:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:48:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:48:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:49:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:50:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:51:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:52:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:53:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:53:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:54:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:55:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:56:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:56:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:57:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2065,7 +2665,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>508</v>
+        <v>703</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -2146,7 +2746,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>704</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -2227,9 +2827,11 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4"/>
+        <v>705</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
       <c r="D4"/>
       <c r="F4" s="1" t="s">
         <v>4</v>
@@ -2306,9 +2908,11 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5"/>
+        <v>706</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
       <c r="D5"/>
       <c r="F5" s="1" t="s">
         <v>4</v>
@@ -2385,9 +2989,11 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6"/>
+        <v>707</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
       <c r="D6"/>
       <c r="F6" s="1" t="s">
         <v>4</v>
@@ -2464,9 +3070,11 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7"/>
+        <v>708</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
       <c r="D7"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
@@ -2676,7 +3284,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>493</v>
+        <v>688</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -2757,7 +3365,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>494</v>
+        <v>689</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -2838,7 +3446,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>495</v>
+        <v>690</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -2919,7 +3527,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>496</v>
+        <v>691</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
@@ -3000,7 +3608,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>497</v>
+        <v>692</v>
       </c>
       <c r="C6" t="s">
         <v>74</v>
@@ -3081,7 +3689,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>498</v>
+        <v>693</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
@@ -3297,7 +3905,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>499</v>
+        <v>694</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -3372,7 +3980,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>500</v>
+        <v>695</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -3447,7 +4055,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>501</v>
+        <v>696</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -3525,7 +4133,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>502</v>
+        <v>697</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
@@ -3600,7 +4208,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>503</v>
+        <v>698</v>
       </c>
       <c r="C6" t="s">
         <v>74</v>
@@ -3675,7 +4283,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>504</v>
+        <v>699</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
@@ -3753,7 +4361,7 @@
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>505</v>
+        <v>700</v>
       </c>
       <c r="C8" t="s">
         <v>74</v>
@@ -3828,7 +4436,7 @@
         <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>506</v>
+        <v>701</v>
       </c>
       <c r="C9" t="s">
         <v>74</v>
@@ -3903,7 +4511,7 @@
         <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>507</v>
+        <v>702</v>
       </c>
       <c r="C10" t="s">
         <v>74</v>

--- a/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3004" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="730">
   <si>
     <t>Notes</t>
   </si>
@@ -2165,6 +2165,69 @@
   </si>
   <si>
     <t>Wed Mar 11 06:57:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:49:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:50:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:51:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:52:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:53:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:54:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:55:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:56:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:57:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:58:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:58:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 20:59:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:01:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:02:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:02:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:04:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:05:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:06:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:06:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:07:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:08:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2665,7 +2728,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -2746,7 +2809,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -2827,7 +2890,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -2908,7 +2971,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
@@ -2989,7 +3052,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="C6" t="s">
         <v>74</v>
@@ -3070,7 +3133,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
@@ -3284,7 +3347,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -3365,7 +3428,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>689</v>
+        <v>710</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -3446,7 +3509,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -3527,7 +3590,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
@@ -3608,7 +3671,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
       <c r="C6" t="s">
         <v>74</v>
@@ -3689,7 +3752,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
@@ -3905,7 +3968,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -3980,7 +4043,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -4055,7 +4118,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>696</v>
+        <v>717</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -4133,7 +4196,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>697</v>
+        <v>718</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
@@ -4208,7 +4271,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>698</v>
+        <v>719</v>
       </c>
       <c r="C6" t="s">
         <v>74</v>
@@ -4283,7 +4346,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
@@ -4361,7 +4424,7 @@
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="C8" t="s">
         <v>74</v>
@@ -4436,7 +4499,7 @@
         <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="C9" t="s">
         <v>74</v>
@@ -4511,7 +4574,7 @@
         <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="C10" t="s">
         <v>74</v>

--- a/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="778">
   <si>
     <t>Notes</t>
   </si>
@@ -2228,6 +2228,150 @@
   </si>
   <si>
     <t>Wed Apr 22 21:08:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:40:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:41:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:42:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:56:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:57:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:57:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:58:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:59:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 23:59:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:00:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:01:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:02:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:03:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:04:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:05:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:06:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:07:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:08:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:09:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:09:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:11:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:12:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:13:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:14:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:15:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:16:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:09:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:10:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:11:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:11:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:12:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:13:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:14:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:15:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:15:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:16:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:17:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:18:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:18:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:19:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:20:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:21:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:22:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:22:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:23:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:24:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:25:01 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2728,7 +2872,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>724</v>
+        <v>772</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -2809,7 +2953,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>725</v>
+        <v>773</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -2890,7 +3034,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>726</v>
+        <v>774</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -2971,7 +3115,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>727</v>
+        <v>775</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
@@ -3052,7 +3196,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="C6" t="s">
         <v>74</v>
@@ -3133,7 +3277,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>729</v>
+        <v>777</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
@@ -3347,7 +3491,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>709</v>
+        <v>757</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -3428,7 +3572,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>710</v>
+        <v>758</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -3509,7 +3653,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>711</v>
+        <v>759</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -3590,7 +3734,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>712</v>
+        <v>760</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
@@ -3671,7 +3815,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>713</v>
+        <v>761</v>
       </c>
       <c r="C6" t="s">
         <v>74</v>
@@ -3752,7 +3896,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>714</v>
+        <v>762</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
@@ -3968,7 +4112,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>715</v>
+        <v>763</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
@@ -4043,7 +4187,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>716</v>
+        <v>764</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
@@ -4118,7 +4262,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>717</v>
+        <v>765</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -4196,7 +4340,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>718</v>
+        <v>766</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
@@ -4271,7 +4415,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>719</v>
+        <v>767</v>
       </c>
       <c r="C6" t="s">
         <v>74</v>
@@ -4346,7 +4490,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>720</v>
+        <v>768</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
@@ -4424,7 +4568,7 @@
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>721</v>
+        <v>769</v>
       </c>
       <c r="C8" t="s">
         <v>74</v>
@@ -4499,7 +4643,7 @@
         <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>722</v>
+        <v>770</v>
       </c>
       <c r="C9" t="s">
         <v>74</v>
@@ -4574,7 +4718,7 @@
         <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>723</v>
+        <v>771</v>
       </c>
       <c r="C10" t="s">
         <v>74</v>

--- a/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3322" uniqueCount="799">
   <si>
     <t>Notes</t>
   </si>
@@ -2372,6 +2372,69 @@
   </si>
   <si>
     <t>Wed Jun 17 00:25:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:11:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:11:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:12:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:12:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:13:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:13:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:13:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:14:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:14:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:14:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:24:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:24:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:25:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:25:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:26:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:26:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:27:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:27:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:27:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:28:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:28:30 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -2745,7 +2808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B298DDF7-645C-408C-A674-CC46C88D47EC}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr defaultColWidth="42.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
@@ -2868,16 +2931,16 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>772</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="1">
+        <v>793</v>
+      </c>
+      <c r="C2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2949,16 +3012,16 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>773</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="1">
+        <v>794</v>
+      </c>
+      <c r="C3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3030,16 +3093,16 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="1">
+        <v>795</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D4"/>
+      <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
@@ -3111,16 +3174,16 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>775</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="1">
+        <v>796</v>
+      </c>
+      <c r="C5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D5"/>
+      <c r="D5" s="1"/>
       <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3192,16 +3255,16 @@
       </c>
     </row>
     <row ht="43.2" r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
-        <v>776</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s" s="1">
+        <v>797</v>
+      </c>
+      <c r="C6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D6"/>
+      <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3273,16 +3336,16 @@
       </c>
     </row>
     <row ht="43.2" r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>777</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s" s="1">
+        <v>798</v>
+      </c>
+      <c r="C7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D7"/>
+      <c r="D7" s="1"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3364,7 +3427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1343EF54-4827-416A-A016-C445805C86F0}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr defaultColWidth="42.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
@@ -3487,16 +3550,16 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="1">
+        <v>778</v>
+      </c>
+      <c r="C2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3568,16 +3631,16 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>758</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="1">
+        <v>779</v>
+      </c>
+      <c r="C3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3649,16 +3712,16 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>759</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="1">
+        <v>780</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D4"/>
+      <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
@@ -3730,16 +3793,16 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>760</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="1">
+        <v>781</v>
+      </c>
+      <c r="C5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D5"/>
+      <c r="D5" s="1"/>
       <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3811,16 +3874,16 @@
       </c>
     </row>
     <row ht="43.2" r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
-        <v>761</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s" s="1">
+        <v>782</v>
+      </c>
+      <c r="C6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D6"/>
+      <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3892,16 +3955,16 @@
       </c>
     </row>
     <row ht="43.2" r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>762</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s" s="1">
+        <v>783</v>
+      </c>
+      <c r="C7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D7"/>
+      <c r="D7" s="1"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3982,7 +4045,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B3AC86-4723-49D7-AB53-411E6A25C44B}">
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr defaultColWidth="42.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="11.21875" collapsed="true"/>
@@ -4108,16 +4171,16 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="1">
+        <v>784</v>
+      </c>
+      <c r="C2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4183,16 +4246,16 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>764</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="1">
+        <v>785</v>
+      </c>
+      <c r="C3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
@@ -4258,16 +4321,16 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>765</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="1">
+        <v>786</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D4"/>
+      <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
@@ -4336,16 +4399,16 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>787</v>
+      </c>
+      <c r="C5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>766</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5"/>
+      <c r="D5" s="1"/>
       <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
@@ -4411,16 +4474,16 @@
       </c>
     </row>
     <row ht="43.2" r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
-        <v>767</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s" s="1">
+        <v>788</v>
+      </c>
+      <c r="C6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D6"/>
+      <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
@@ -4486,16 +4549,16 @@
       </c>
     </row>
     <row ht="43.2" r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>768</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s" s="1">
+        <v>789</v>
+      </c>
+      <c r="C7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D7"/>
+      <c r="D7" s="1"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
@@ -4564,16 +4627,16 @@
       </c>
     </row>
     <row ht="43.2" r="8" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
-        <v>769</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" t="s" s="1">
+        <v>790</v>
+      </c>
+      <c r="C8" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D8"/>
+      <c r="D8" s="1"/>
       <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
@@ -4639,16 +4702,16 @@
       </c>
     </row>
     <row ht="43.2" r="9" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B9" t="s">
-        <v>770</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" t="s" s="1">
+        <v>791</v>
+      </c>
+      <c r="C9" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D9"/>
+      <c r="D9" s="1"/>
       <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
@@ -4714,16 +4777,16 @@
       </c>
     </row>
     <row ht="43.2" r="10" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B10" t="s">
-        <v>771</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" t="s" s="1">
+        <v>792</v>
+      </c>
+      <c r="C10" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D10"/>
+      <c r="D10" s="1"/>
       <c r="F10" s="1" t="s">
         <v>4</v>
       </c>

--- a/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Payments-Data-Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3490" uniqueCount="883">
   <si>
     <t>Notes</t>
   </si>
@@ -2372,6 +2372,321 @@
   </si>
   <si>
     <t>Wed Jun 17 00:25:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:35:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:36:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:37:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:37:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:38:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:39:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:40:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:40:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:41:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:42:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:42:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:43:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:43:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:44:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:45:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:46:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:46:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:47:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:48:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:48:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:49:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:04:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:05:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:06:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:06:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:07:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:08:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:08:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:09:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:09:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:10:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:11:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:12:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:13:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:13:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:14:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:15:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:15:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:16:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:17:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:17:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 16:58:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 16:59:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:00:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:01:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:02:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:03:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:03:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:04:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:05:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:06:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:07:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:07:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:08:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:09:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:10:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:11:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:12:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:13:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:13:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:14:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:15:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:28:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:29:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:29:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:30:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:31:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:32:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:33:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:34:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:35:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:36:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:37:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:38:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:38:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:39:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:40:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:41:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:42:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:42:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:43:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:44:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:45:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:26:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:27:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:28:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:29:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:29:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:30:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:31:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:32:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:32:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:33:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:34:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:34:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:36:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:37:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:37:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:38:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:39:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:39:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:40:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:41:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:42:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2745,7 +3060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B298DDF7-645C-408C-A674-CC46C88D47EC}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr defaultColWidth="42.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
@@ -2868,16 +3183,16 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>772</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="1">
+        <v>877</v>
+      </c>
+      <c r="C2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2949,16 +3264,16 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>773</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="1">
+        <v>878</v>
+      </c>
+      <c r="C3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3030,16 +3345,16 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="1">
+        <v>879</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D4"/>
+      <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
@@ -3111,16 +3426,16 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>775</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="1">
+        <v>880</v>
+      </c>
+      <c r="C5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D5"/>
+      <c r="D5" s="1"/>
       <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3192,16 +3507,16 @@
       </c>
     </row>
     <row ht="43.2" r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
-        <v>776</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s" s="1">
+        <v>881</v>
+      </c>
+      <c r="C6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D6"/>
+      <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3273,16 +3588,16 @@
       </c>
     </row>
     <row ht="43.2" r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>777</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s" s="1">
+        <v>882</v>
+      </c>
+      <c r="C7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D7"/>
+      <c r="D7" s="1"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3364,7 +3679,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1343EF54-4827-416A-A016-C445805C86F0}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr defaultColWidth="42.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
@@ -3487,16 +3802,16 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="1">
+        <v>862</v>
+      </c>
+      <c r="C2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3568,16 +3883,16 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>758</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="1">
+        <v>863</v>
+      </c>
+      <c r="C3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3649,16 +3964,16 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>759</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="1">
+        <v>864</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D4"/>
+      <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
@@ -3730,16 +4045,16 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>760</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="1">
+        <v>865</v>
+      </c>
+      <c r="C5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D5"/>
+      <c r="D5" s="1"/>
       <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3811,16 +4126,16 @@
       </c>
     </row>
     <row ht="43.2" r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
-        <v>761</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s" s="1">
+        <v>866</v>
+      </c>
+      <c r="C6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D6"/>
+      <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
@@ -3892,16 +4207,16 @@
       </c>
     </row>
     <row ht="43.2" r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>762</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s" s="1">
+        <v>867</v>
+      </c>
+      <c r="C7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D7"/>
+      <c r="D7" s="1"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3982,7 +4297,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B3AC86-4723-49D7-AB53-411E6A25C44B}">
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr defaultColWidth="42.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="11.21875" collapsed="true"/>
@@ -4108,16 +4423,16 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="1">
+        <v>868</v>
+      </c>
+      <c r="C2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4183,16 +4498,16 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>764</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="1">
+        <v>869</v>
+      </c>
+      <c r="C3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
@@ -4258,16 +4573,16 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>765</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="1">
+        <v>870</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D4"/>
+      <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
@@ -4336,16 +4651,16 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>766</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="1">
+        <v>871</v>
+      </c>
+      <c r="C5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D5"/>
+      <c r="D5" s="1"/>
       <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
@@ -4411,16 +4726,16 @@
       </c>
     </row>
     <row ht="43.2" r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
-        <v>767</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s" s="1">
+        <v>872</v>
+      </c>
+      <c r="C6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D6"/>
+      <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
@@ -4486,16 +4801,16 @@
       </c>
     </row>
     <row ht="43.2" r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>768</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" t="s" s="1">
+        <v>873</v>
+      </c>
+      <c r="C7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D7"/>
+      <c r="D7" s="1"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
@@ -4564,16 +4879,16 @@
       </c>
     </row>
     <row ht="43.2" r="8" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
-        <v>769</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" t="s" s="1">
+        <v>874</v>
+      </c>
+      <c r="C8" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D8"/>
+      <c r="D8" s="1"/>
       <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
@@ -4639,16 +4954,16 @@
       </c>
     </row>
     <row ht="43.2" r="9" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B9" t="s">
-        <v>770</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" t="s" s="1">
+        <v>875</v>
+      </c>
+      <c r="C9" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D9"/>
+      <c r="D9" s="1"/>
       <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
@@ -4714,16 +5029,16 @@
       </c>
     </row>
     <row ht="43.2" r="10" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B10" t="s">
-        <v>771</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" t="s" s="1">
+        <v>876</v>
+      </c>
+      <c r="C10" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="D10"/>
+      <c r="D10" s="1"/>
       <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
